--- a/demo/FICHERO_CARGA_DEMO.xlsx
+++ b/demo/FICHERO_CARGA_DEMO.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
